--- a/data/trans_bre/P12_2_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,23</t>
+          <t>6,46; 15,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 13,16</t>
+          <t>4,34; 13,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,09</t>
+          <t>0,31; 9,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 6,67</t>
+          <t>-1,1; 6,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,87; 97,78</t>
+          <t>31,91; 94,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 94,36</t>
+          <t>23,04; 93,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 56,97</t>
+          <t>1,05; 58,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 36,68</t>
+          <t>-4,86; 36,94</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 16,12</t>
+          <t>7,64; 15,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,09</t>
+          <t>4,77; 12,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,97</t>
+          <t>4,32; 11,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 16,71</t>
+          <t>6,72; 16,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,38; 83,72</t>
+          <t>32,21; 80,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,4; 93,24</t>
+          <t>30,07; 94,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,32; 91,39</t>
+          <t>27,14; 87,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,84; 275,5</t>
+          <t>47,76; 280,99</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,69</t>
+          <t>2,22; 11,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,51</t>
+          <t>1,9; 10,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 9,27</t>
+          <t>1,19; 9,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 7,63</t>
+          <t>-8,71; 7,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,57; 70,54</t>
+          <t>11,5; 78,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 66,69</t>
+          <t>8,59; 66,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 70,77</t>
+          <t>7,08; 68,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 52,78</t>
+          <t>-47,58; 51,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 14,57</t>
+          <t>6,86; 14,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,64</t>
+          <t>4,41; 12,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 11,43</t>
+          <t>4,0; 11,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 8,91</t>
+          <t>-0,38; 9,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,73; 80,54</t>
+          <t>30,9; 82,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,44; 68,36</t>
+          <t>19,89; 66,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 81,57</t>
+          <t>22,46; 81,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 51,37</t>
+          <t>0,27; 50,62</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,2</t>
+          <t>8,19; 12,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,22</t>
+          <t>6,34; 10,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,46</t>
+          <t>4,59; 8,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,17</t>
+          <t>1,97; 9,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,8; 65,85</t>
+          <t>39,95; 65,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,8; 62,21</t>
+          <t>34,54; 63,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,55; 57,18</t>
+          <t>27,75; 58,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,92; 70,41</t>
+          <t>13,01; 67,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_2_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 15,42</t>
+          <t>6,88; 15,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 13,29</t>
+          <t>4,48; 13,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 9,21</t>
+          <t>0,02; 8,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 6,82</t>
+          <t>-1,08; 6,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,91; 94,22</t>
+          <t>31,74; 94,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,04; 93,88</t>
+          <t>24,48; 93,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 58,49</t>
+          <t>-0,07; 55,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 36,94</t>
+          <t>-5,06; 35,09</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,65</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 15,77</t>
+          <t>7,32; 15,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,13</t>
+          <t>4,83; 12,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,38</t>
+          <t>4,62; 11,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 16,45</t>
+          <t>4,31; 10,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,21; 80,29</t>
+          <t>30,49; 79,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,07; 94,68</t>
+          <t>30,17; 97,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,14; 87,8</t>
+          <t>27,94; 90,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,76; 280,99</t>
+          <t>28,49; 87,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,28</t>
+          <t>1,81; 10,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 10,57</t>
+          <t>1,37; 10,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 9,14</t>
+          <t>0,88; 9,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 7,39</t>
+          <t>4,41; 12,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,5; 78,26</t>
+          <t>9,17; 72,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 66,15</t>
+          <t>5,81; 66,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 68,65</t>
+          <t>5,3; 69,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 51,29</t>
+          <t>23,61; 91,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 14,83</t>
+          <t>6,51; 14,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 12,43</t>
+          <t>4,89; 12,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,36</t>
+          <t>4,33; 11,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,05</t>
+          <t>3,03; 9,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,9; 82,62</t>
+          <t>29,97; 78,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,89; 66,79</t>
+          <t>21,17; 68,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,46; 81,01</t>
+          <t>24,53; 83,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 50,62</t>
+          <t>14,3; 55,95</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,3</t>
+          <t>8,19; 12,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,22</t>
+          <t>6,13; 10,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,48</t>
+          <t>4,64; 8,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,01</t>
+          <t>4,71; 8,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,95; 65,62</t>
+          <t>40,29; 65,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,54; 63,0</t>
+          <t>33,59; 61,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,75; 58,56</t>
+          <t>27,52; 57,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,01; 67,96</t>
+          <t>26,29; 52,0</t>
         </is>
       </c>
     </row>
